--- a/results/raw_code_ud.xlsx
+++ b/results/raw_code_ud.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dalhousie\Desktop\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F0244-93B5-43B3-8260-650FD010D127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DE68B9-A004-481F-A21C-3DDE1A4B8F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CEF30AF1-C0FA-444E-A5F8-C0020D3AD9A8}"/>
   </bookViews>
@@ -2297,6 +2297,7 @@
     <col min="4" max="4" width="126" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="11.28515625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2470,7 +2471,7 @@
         <v>149</v>
       </c>
       <c r="E6" s="3">
-        <v>25085</v>
+        <v>5207</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -2598,7 +2599,7 @@
         <v>36</v>
       </c>
       <c r="E10" s="3">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -2662,7 +2663,7 @@
         <v>57</v>
       </c>
       <c r="E12" s="3">
-        <v>38494</v>
+        <v>5611</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -2694,7 +2695,7 @@
         <v>185</v>
       </c>
       <c r="E13" s="3">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -2758,7 +2759,7 @@
         <v>42</v>
       </c>
       <c r="E15" s="3">
-        <v>85742</v>
+        <v>4081</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -2822,7 +2823,7 @@
         <v>13</v>
       </c>
       <c r="E17" s="3">
-        <v>88854</v>
+        <v>16042</v>
       </c>
       <c r="F17" s="3">
         <v>0</v>
@@ -2886,7 +2887,7 @@
         <v>204</v>
       </c>
       <c r="E19" s="3">
-        <v>57631</v>
+        <v>1227</v>
       </c>
       <c r="F19" s="3">
         <v>0</v>
@@ -2982,7 +2983,7 @@
         <v>71</v>
       </c>
       <c r="E22" s="3">
-        <v>26964</v>
+        <v>1858</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -3014,7 +3015,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="3">
-        <v>71512</v>
+        <v>6948</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
@@ -3078,7 +3079,7 @@
         <v>110</v>
       </c>
       <c r="E25" s="3">
-        <v>77832</v>
+        <v>1000</v>
       </c>
       <c r="F25" s="3">
         <v>0</v>
@@ -3142,7 +3143,7 @@
         <v>187</v>
       </c>
       <c r="E27" s="3">
-        <v>79550</v>
+        <v>2102</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
@@ -3270,7 +3271,7 @@
         <v>173</v>
       </c>
       <c r="E31" s="3">
-        <v>46574</v>
+        <v>490</v>
       </c>
       <c r="F31" s="3">
         <v>0</v>
@@ -3366,7 +3367,7 @@
         <v>131</v>
       </c>
       <c r="E34" s="3">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="F34" s="3">
         <v>0</v>
@@ -3462,7 +3463,7 @@
         <v>52</v>
       </c>
       <c r="E37" s="3">
-        <v>92728</v>
+        <v>4452</v>
       </c>
       <c r="F37" s="3">
         <v>0</v>
@@ -3622,7 +3623,7 @@
         <v>133</v>
       </c>
       <c r="E42" s="3">
-        <v>76987</v>
+        <v>6355</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3718,7 +3719,7 @@
         <v>21</v>
       </c>
       <c r="E45" s="3">
-        <v>82637</v>
+        <v>2636</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -3878,7 +3879,7 @@
         <v>141</v>
       </c>
       <c r="E50" s="3">
-        <v>99702</v>
+        <v>14543</v>
       </c>
       <c r="F50" s="3">
         <v>0</v>
@@ -3974,7 +3975,7 @@
         <v>165</v>
       </c>
       <c r="E53" s="3">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F53" s="3">
         <v>0</v>
@@ -4102,7 +4103,7 @@
         <v>118</v>
       </c>
       <c r="E57" s="3">
-        <v>27968</v>
+        <v>4052</v>
       </c>
       <c r="F57" s="3">
         <v>1</v>
@@ -4198,7 +4199,7 @@
         <v>75</v>
       </c>
       <c r="E60" s="3">
-        <v>16467</v>
+        <v>15499</v>
       </c>
       <c r="F60" s="3">
         <v>0</v>
@@ -4294,7 +4295,7 @@
         <v>38</v>
       </c>
       <c r="E63" s="3">
-        <v>27218</v>
+        <v>1447</v>
       </c>
       <c r="F63" s="3">
         <v>0</v>
@@ -4614,7 +4615,7 @@
         <v>59</v>
       </c>
       <c r="E73" s="3">
-        <v>82682</v>
+        <v>12974</v>
       </c>
       <c r="F73" s="3">
         <v>0</v>
@@ -4646,7 +4647,7 @@
         <v>106</v>
       </c>
       <c r="E74" s="3">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="F74" s="3">
         <v>0</v>
@@ -4806,7 +4807,7 @@
         <v>143</v>
       </c>
       <c r="E79" s="3">
-        <v>1099</v>
+        <v>475</v>
       </c>
       <c r="F79" s="3">
         <v>0</v>
@@ -4966,7 +4967,7 @@
         <v>138</v>
       </c>
       <c r="E84" s="3">
-        <v>48146</v>
+        <v>455</v>
       </c>
       <c r="F84" s="3">
         <v>0</v>
@@ -5094,7 +5095,7 @@
         <v>98</v>
       </c>
       <c r="E88" s="3">
-        <v>43405</v>
+        <v>709</v>
       </c>
       <c r="F88" s="3">
         <v>0</v>
@@ -5190,7 +5191,7 @@
         <v>169</v>
       </c>
       <c r="E91" s="3">
-        <v>27775</v>
+        <v>624</v>
       </c>
       <c r="F91" s="3">
         <v>1</v>
@@ -5286,7 +5287,7 @@
         <v>212</v>
       </c>
       <c r="E94" s="3">
-        <v>20618</v>
+        <v>3305</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -5318,7 +5319,7 @@
         <v>153</v>
       </c>
       <c r="E95" s="3">
-        <v>96878</v>
+        <v>1222</v>
       </c>
       <c r="F95" s="3">
         <v>0</v>
@@ -5350,7 +5351,7 @@
         <v>123</v>
       </c>
       <c r="E96" s="3">
-        <v>16869</v>
+        <v>2056</v>
       </c>
       <c r="F96" s="3">
         <v>1</v>
@@ -5382,7 +5383,7 @@
         <v>177</v>
       </c>
       <c r="E97" s="3">
-        <v>59626</v>
+        <v>11118</v>
       </c>
       <c r="F97" s="3">
         <v>0</v>
@@ -5478,7 +5479,7 @@
         <v>125</v>
       </c>
       <c r="E100" s="3">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
